--- a/Result/profitability/5348.xlsx
+++ b/Result/profitability/5348.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2775</v>
+        <v>-0.255</v>
       </c>
       <c r="N2" t="n">
-        <v>28.77625</v>
+        <v>29.06125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.17625</v>
+        <v>-0.23125</v>
       </c>
       <c r="N3" t="n">
-        <v>29.96875</v>
+        <v>29.6725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.14625</v>
+        <v>-0.13125</v>
       </c>
       <c r="N4" t="n">
-        <v>30.7225</v>
+        <v>30.48875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.055</v>
+        <v>-0.03750000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>31.8225</v>
+        <v>31.65875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0375</v>
+        <v>0.02749999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>32.6925</v>
+        <v>32.26375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003750000000000003</v>
+        <v>0.0275</v>
       </c>
       <c r="N7" t="n">
-        <v>32.72875000000001</v>
+        <v>31.975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01125</v>
+        <v>0.004999999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>32.83875</v>
+        <v>32.3775</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9341,14 +9341,14 @@
         <v>16</v>
       </c>
       <c r="F71" t="n">
-        <v>27.96</v>
+        <v>27.18</v>
       </c>
       <c r="G71" t="n">
         <v>-2</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-3.24%</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -9367,7 +9367,7 @@
         <v>-0.1575</v>
       </c>
       <c r="N71" t="n">
-        <v>25.8625</v>
+        <v>25.765</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9400,10 +9400,10 @@
         <v>0.04999999999999982</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.2200000000000024</v>
+        <v>-0.5599999999999987</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.007930785868781598</v>
+        <v>-0.02018745493871665</v>
       </c>
       <c r="AA71" t="n">
         <v>-0.33</v>
@@ -9412,10 +9412,10 @@
         <v>3.666666666666667</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.620000000000001</v>
+        <v>0.8399999999999999</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.06150341685649208</v>
+        <v>0.03189066059225509</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
         <v>1</v>
@@ -9494,7 +9494,7 @@
         <v>-0.19375</v>
       </c>
       <c r="N72" t="n">
-        <v>26.59375</v>
+        <v>26.49625</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9527,10 +9527,10 @@
         <v>-0.5238095238095237</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.119999999999997</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.07582260371959926</v>
+        <v>0.1066961000735835</v>
       </c>
       <c r="AA72" t="n">
         <v>0.26</v>
@@ -9621,7 +9621,7 @@
         <v>-0.25125</v>
       </c>
       <c r="N73" t="n">
-        <v>27.57</v>
+        <v>27.4725</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9748,7 +9748,7 @@
         <v>-0.26375</v>
       </c>
       <c r="N74" t="n">
-        <v>28.37125</v>
+        <v>28.27375</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>75</v>
+      </c>
+      <c r="D75" t="n">
+        <v>55</v>
+      </c>
+      <c r="E75" t="n">
+        <v>20</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.3125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.05000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2173913043478262</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.690000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1216216216216217</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5300000000000011</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01949963208241356</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
